--- a/results/nhanes__race-ethnicity__routine-blood-tests/results.xlsx
+++ b/results/nhanes__race-ethnicity__routine-blood-tests/results.xlsx
@@ -24,8 +24,8 @@
     <sheet name="select" sheetId="15" r:id="rId15"/>
     <sheet name="select_picks_summary" sheetId="16" r:id="rId16"/>
     <sheet name="pareto" sheetId="17" r:id="rId17"/>
-    <sheet name="external" sheetId="18" r:id="rId18"/>
-    <sheet name="shap_by_group" sheetId="19" r:id="rId19"/>
+    <sheet name="shap_by_group" sheetId="18" r:id="rId18"/>
+    <sheet name="lime_shap_agreement" sheetId="19" r:id="rId19"/>
     <sheet name="label_bias" sheetId="20" r:id="rId20"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="856" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="390">
   <si>
     <t>Value</t>
   </si>
@@ -683,171 +683,261 @@
     <t>Reweighing (pre-processing)</t>
   </si>
   <si>
+    <t>Group-balanced SMOTE (pre-processing)</t>
+  </si>
+  <si>
     <t>Exponentiated Gradient (in-processing)</t>
   </si>
   <si>
     <t>Threshold Optimizer (post-processing)</t>
   </si>
   <si>
+    <t>Reject Option Classification (post-processing)</t>
+  </si>
+  <si>
     <t>Reweighing + Threshold Optimizer (hybrid)</t>
   </si>
   <si>
+    <t>0.729 ± 0.002</t>
+  </si>
+  <si>
     <t>0.745 ± 0.003</t>
   </si>
   <si>
     <t>0.748 ± 0.021</t>
   </si>
   <si>
+    <t>0.740 ± 0.004</t>
+  </si>
+  <si>
     <t>0.751 ± 0.015</t>
   </si>
   <si>
     <t>0.773 ± 0.003</t>
   </si>
   <si>
+    <t>0.824 ± 0.003</t>
+  </si>
+  <si>
     <t>0.791 ± 0.003</t>
   </si>
   <si>
     <t>0.739 ± 0.025</t>
   </si>
   <si>
+    <t>0.762 ± 0.005</t>
+  </si>
+  <si>
     <t>0.736 ± 0.013</t>
   </si>
   <si>
     <t>0.734 ± 0.002</t>
   </si>
   <si>
+    <t>0.730 ± 0.002</t>
+  </si>
+  <si>
     <t>0.720 ± 0.005</t>
   </si>
   <si>
     <t>0.683 ± 0.005</t>
   </si>
   <si>
+    <t>0.724 ± 0.003</t>
+  </si>
+  <si>
     <t>0.685 ± 0.006</t>
   </si>
   <si>
+    <t>0.704 ± 0.008</t>
+  </si>
+  <si>
     <t>0.729 ± 0.005</t>
   </si>
   <si>
     <t>0.683 ± 0.010</t>
   </si>
   <si>
+    <t>0.731 ± 0.002</t>
+  </si>
+  <si>
     <t>0.682 ± 0.009</t>
   </si>
   <si>
     <t>0.709 ± 0.004</t>
   </si>
   <si>
+    <t>0.731 ± 0.003</t>
+  </si>
+  <si>
     <t>0.681 ± 0.009</t>
   </si>
   <si>
     <t>0.579 ± 0.033</t>
   </si>
   <si>
+    <t>0.698 ± 0.005</t>
+  </si>
+  <si>
     <t>0.582 ± 0.016</t>
   </si>
   <si>
     <t>0.671 ± 0.002</t>
   </si>
   <si>
+    <t>0.512 ± 0.016</t>
+  </si>
+  <si>
     <t>0.630 ± 0.008</t>
   </si>
   <si>
     <t>0.595 ± 0.049</t>
   </si>
   <si>
+    <t>0.681 ± 0.003</t>
+  </si>
+  <si>
     <t>0.597 ± 0.025</t>
   </si>
   <si>
     <t>0.513 ± 0.003</t>
   </si>
   <si>
+    <t>0.500 ± 0.002</t>
+  </si>
+  <si>
     <t>0.497 ± 0.006</t>
   </si>
   <si>
     <t>0.460 ± 0.010</t>
   </si>
   <si>
+    <t>0.499 ± 0.005</t>
+  </si>
+  <si>
     <t>0.464 ± 0.011</t>
   </si>
   <si>
     <t>0.524 ± 0.003</t>
   </si>
   <si>
+    <t>0.519 ± 0.011</t>
+  </si>
+  <si>
     <t>0.528 ± 0.007</t>
   </si>
   <si>
     <t>0.458 ± 0.013</t>
   </si>
   <si>
+    <t>0.515 ± 0.004</t>
+  </si>
+  <si>
     <t>0.456 ± 0.011</t>
   </si>
   <si>
     <t>0.126 ± 0.009</t>
   </si>
   <si>
+    <t>0.126 ± 0.007</t>
+  </si>
+  <si>
     <t>0.078 ± 0.009</t>
   </si>
   <si>
     <t>0.037 ± 0.016</t>
   </si>
   <si>
+    <t>0.051 ± 0.010</t>
+  </si>
+  <si>
     <t>0.036 ± 0.009</t>
   </si>
   <si>
+    <t>0.113 ± 0.006</t>
+  </si>
+  <si>
     <t>0.103 ± 0.009</t>
   </si>
   <si>
     <t>0.043 ± 0.021</t>
   </si>
   <si>
+    <t>0.063 ± 0.036</t>
+  </si>
+  <si>
     <t>0.051 ± 0.011</t>
   </si>
   <si>
     <t>0.662 ± 0.022</t>
   </si>
   <si>
+    <t>0.689 ± 0.019</t>
+  </si>
+  <si>
     <t>0.779 ± 0.025</t>
   </si>
   <si>
     <t>0.874 ± 0.058</t>
   </si>
   <si>
+    <t>0.857 ± 0.029</t>
+  </si>
+  <si>
     <t>0.878 ± 0.035</t>
   </si>
   <si>
     <t>0.644 ± 0.026</t>
   </si>
   <si>
+    <t>0.526 ± 0.018</t>
+  </si>
+  <si>
     <t>0.656 ± 0.027</t>
   </si>
   <si>
     <t>0.862 ± 0.064</t>
   </si>
   <si>
+    <t>0.817 ± 0.097</t>
+  </si>
+  <si>
     <t>0.841 ± 0.037</t>
   </si>
   <si>
     <t>0.232 ± 0.024</t>
   </si>
   <si>
+    <t>0.211 ± 0.019</t>
+  </si>
+  <si>
     <t>0.090 ± 0.038</t>
   </si>
   <si>
     <t>0.077 ± 0.027</t>
   </si>
   <si>
+    <t>0.109 ± 0.022</t>
+  </si>
+  <si>
     <t>0.098 ± 0.023</t>
   </si>
   <si>
     <t>0.238 ± 0.018</t>
   </si>
   <si>
+    <t>0.230 ± 0.016</t>
+  </si>
+  <si>
     <t>0.222 ± 0.014</t>
   </si>
   <si>
     <t>0.095 ± 0.047</t>
   </si>
   <si>
+    <t>0.143 ± 0.026</t>
+  </si>
+  <si>
     <t>0.116 ± 0.071</t>
   </si>
   <si>
@@ -857,51 +947,78 @@
     <t>0.079 ± 0.025</t>
   </si>
   <si>
+    <t>0.116 ± 0.014</t>
+  </si>
+  <si>
     <t>0.151 ± 0.005</t>
   </si>
   <si>
+    <t>0.156 ± 0.009</t>
+  </si>
+  <si>
     <t>0.161 ± 0.011</t>
   </si>
   <si>
     <t>0.139 ± 0.013</t>
   </si>
   <si>
+    <t>0.216 ± 0.025</t>
+  </si>
+  <si>
     <t>0.155 ± 0.017</t>
   </si>
   <si>
     <t>0.158 ± 0.016</t>
   </si>
   <si>
+    <t>0.244 ± 0.014</t>
+  </si>
+  <si>
     <t>0.175 ± 0.014</t>
   </si>
   <si>
     <t>0.172 ± 0.015</t>
   </si>
   <si>
+    <t>0.213 ± 0.015</t>
+  </si>
+  <si>
     <t>0.150 ± 0.019</t>
   </si>
   <si>
     <t>0.032 ± 0.007</t>
   </si>
   <si>
+    <t>0.038 ± 0.010</t>
+  </si>
+  <si>
     <t>0.049 ± 0.011</t>
   </si>
   <si>
     <t>0.034 ± 0.017</t>
   </si>
   <si>
+    <t>0.075 ± 0.007</t>
+  </si>
+  <si>
     <t>0.038 ± 0.020</t>
   </si>
   <si>
     <t>0.049 ± 0.010</t>
   </si>
   <si>
+    <t>0.038 ± 0.009</t>
+  </si>
+  <si>
     <t>0.040 ± 0.014</t>
   </si>
   <si>
     <t>0.038 ± 0.007</t>
   </si>
   <si>
+    <t>0.057 ± 0.009</t>
+  </si>
+  <si>
     <t>Δ EOdds gap</t>
   </si>
   <si>
@@ -923,54 +1040,81 @@
     <t>Reweighing</t>
   </si>
   <si>
+    <t>SMOTE</t>
+  </si>
+  <si>
     <t>Exp. Gradient</t>
   </si>
   <si>
     <t>Threshold Opt.</t>
   </si>
   <si>
+    <t>Reject Option</t>
+  </si>
+  <si>
     <t>RW + TO (hybrid)</t>
   </si>
   <si>
     <t>[-0.025, 0.057]</t>
   </si>
   <si>
+    <t>[-0.060, 0.068]</t>
+  </si>
+  <si>
     <t>[-0.180, 0.024]</t>
   </si>
   <si>
     <t>[-0.206, 0.034]</t>
   </si>
   <si>
+    <t>[-0.125, -0.008]</t>
+  </si>
+  <si>
     <t>[-0.227, 0.093]</t>
   </si>
   <si>
     <t>[-0.071, 0.022]</t>
   </si>
   <si>
+    <t>[-0.122, 0.129]</t>
+  </si>
+  <si>
     <t>[-0.098, 0.028]</t>
   </si>
   <si>
     <t>[-0.210, 0.073]</t>
   </si>
   <si>
+    <t>[-0.146, 0.011]</t>
+  </si>
+  <si>
     <t>[-0.194, 0.114]</t>
   </si>
   <si>
     <t>[-0.009, 0.001]</t>
   </si>
   <si>
+    <t>[-0.016, -0.001]</t>
+  </si>
+  <si>
     <t>[-0.025, 0.001]</t>
   </si>
   <si>
     <t>[-0.066, -0.039]</t>
   </si>
   <si>
+    <t>[-0.023, -0.005]</t>
+  </si>
+  <si>
     <t>[-0.071, -0.044]</t>
   </si>
   <si>
     <t>[-0.008, 0.008]</t>
   </si>
   <si>
+    <t>[-0.044, -0.016]</t>
+  </si>
+  <si>
     <t>[-0.018, 0.001]</t>
   </si>
   <si>
@@ -1001,28 +1145,28 @@
     <t>Accuracy-driven selection</t>
   </si>
   <si>
+    <t>0.744 ± 0.001</t>
+  </si>
+  <si>
     <t>0.755 ± 0.000</t>
   </si>
   <si>
-    <t>0.719 ± 0.004</t>
+    <t>0.721 ± 0.001</t>
   </si>
   <si>
     <t>0.733 ± 0.002</t>
   </si>
   <si>
-    <t>0.669 ± 0.012</t>
-  </si>
-  <si>
-    <t>0.698 ± 0.005</t>
-  </si>
-  <si>
-    <t>0.128 ± 0.056</t>
+    <t>0.685 ± 0.002</t>
+  </si>
+  <si>
+    <t>0.113 ± 0.018</t>
   </si>
   <si>
     <t>0.220 ± 0.022</t>
   </si>
   <si>
-    <t>0.083 ± 0.012</t>
+    <t>0.067 ± 0.003</t>
   </si>
   <si>
     <t>0.120 ± 0.003</t>
@@ -1035,6 +1179,12 @@
   </si>
   <si>
     <t>Overall</t>
+  </si>
+  <si>
+    <t>Mean top-5 overlap (of 5)</t>
+  </si>
+  <si>
+    <t>Mean LIME local R2</t>
   </si>
   <si>
     <t>Adults</t>
@@ -3490,7 +3640,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -3577,31 +3727,31 @@
         <v>82</v>
       </c>
       <c r="D3" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="E3" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F3" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="G3" t="s">
-        <v>249</v>
+        <v>267</v>
       </c>
       <c r="H3" t="s">
-        <v>256</v>
+        <v>278</v>
       </c>
       <c r="I3" t="s">
-        <v>264</v>
+        <v>290</v>
       </c>
       <c r="J3" t="s">
-        <v>264</v>
+        <v>290</v>
       </c>
       <c r="K3" t="s">
-        <v>274</v>
+        <v>305</v>
       </c>
       <c r="L3" t="s">
-        <v>282</v>
+        <v>317</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -3609,34 +3759,34 @@
         <v>216</v>
       </c>
       <c r="C4" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D4" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="E4" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="F4" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="G4" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="H4" t="s">
-        <v>257</v>
+        <v>279</v>
       </c>
       <c r="I4" t="s">
-        <v>265</v>
+        <v>291</v>
       </c>
       <c r="J4" t="s">
-        <v>272</v>
+        <v>291</v>
       </c>
       <c r="K4" t="s">
-        <v>275</v>
+        <v>306</v>
       </c>
       <c r="L4" t="s">
-        <v>283</v>
+        <v>318</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -3644,34 +3794,34 @@
         <v>217</v>
       </c>
       <c r="C5" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D5" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="E5" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="F5" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="G5" t="s">
-        <v>251</v>
+        <v>269</v>
       </c>
       <c r="H5" t="s">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="I5" t="s">
-        <v>266</v>
+        <v>292</v>
       </c>
       <c r="J5" t="s">
-        <v>273</v>
+        <v>302</v>
       </c>
       <c r="K5" t="s">
-        <v>276</v>
+        <v>307</v>
       </c>
       <c r="L5" t="s">
-        <v>284</v>
+        <v>319</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -3679,218 +3829,358 @@
         <v>218</v>
       </c>
       <c r="C6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D6" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="E6" t="s">
+        <v>246</v>
+      </c>
+      <c r="F6" t="s">
+        <v>258</v>
+      </c>
+      <c r="G6" t="s">
+        <v>270</v>
+      </c>
+      <c r="H6" t="s">
+        <v>281</v>
+      </c>
+      <c r="I6" t="s">
+        <v>293</v>
+      </c>
+      <c r="J6" t="s">
+        <v>303</v>
+      </c>
+      <c r="K6" t="s">
+        <v>308</v>
+      </c>
+      <c r="L6" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="B7" t="s">
+        <v>219</v>
+      </c>
+      <c r="C7" t="s">
+        <v>224</v>
+      </c>
+      <c r="D7" t="s">
         <v>236</v>
       </c>
-      <c r="F6" t="s">
-        <v>244</v>
-      </c>
-      <c r="G6" t="s">
-        <v>252</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="E7" t="s">
+        <v>247</v>
+      </c>
+      <c r="F7" t="s">
         <v>259</v>
       </c>
-      <c r="I6" t="s">
-        <v>267</v>
-      </c>
-      <c r="J6" t="s">
-        <v>267</v>
-      </c>
-      <c r="K6" t="s">
-        <v>277</v>
-      </c>
-      <c r="L6" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" t="s">
-        <v>81</v>
-      </c>
-      <c r="B7" t="s">
-        <v>214</v>
-      </c>
-      <c r="C7" t="s">
-        <v>88</v>
-      </c>
-      <c r="D7" t="s">
-        <v>123</v>
-      </c>
-      <c r="E7" t="s">
-        <v>102</v>
-      </c>
-      <c r="F7" t="s">
-        <v>109</v>
-      </c>
       <c r="G7" t="s">
-        <v>137</v>
+        <v>271</v>
       </c>
       <c r="H7" t="s">
-        <v>145</v>
+        <v>282</v>
       </c>
       <c r="I7" t="s">
-        <v>153</v>
+        <v>294</v>
       </c>
       <c r="J7" t="s">
-        <v>153</v>
+        <v>304</v>
       </c>
       <c r="K7" t="s">
-        <v>161</v>
+        <v>309</v>
       </c>
       <c r="L7" t="s">
-        <v>168</v>
+        <v>321</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="B8" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="C8" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D8" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="E8" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="F8" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="G8" t="s">
-        <v>133</v>
+        <v>272</v>
       </c>
       <c r="H8" t="s">
-        <v>260</v>
+        <v>283</v>
       </c>
       <c r="I8" t="s">
-        <v>268</v>
+        <v>295</v>
       </c>
       <c r="J8" t="s">
-        <v>268</v>
+        <v>295</v>
       </c>
       <c r="K8" t="s">
-        <v>278</v>
+        <v>310</v>
       </c>
       <c r="L8" t="s">
-        <v>286</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9" spans="1:12">
+      <c r="A9" t="s">
+        <v>81</v>
+      </c>
       <c r="B9" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C9" t="s">
-        <v>223</v>
+        <v>88</v>
       </c>
       <c r="D9" t="s">
-        <v>230</v>
+        <v>123</v>
       </c>
       <c r="E9" t="s">
-        <v>238</v>
+        <v>102</v>
       </c>
       <c r="F9" t="s">
-        <v>246</v>
+        <v>109</v>
       </c>
       <c r="G9" t="s">
-        <v>253</v>
+        <v>137</v>
       </c>
       <c r="H9" t="s">
-        <v>261</v>
+        <v>145</v>
       </c>
       <c r="I9" t="s">
-        <v>269</v>
+        <v>153</v>
       </c>
       <c r="J9" t="s">
-        <v>269</v>
+        <v>153</v>
       </c>
       <c r="K9" t="s">
-        <v>279</v>
+        <v>161</v>
       </c>
       <c r="L9" t="s">
-        <v>287</v>
+        <v>168</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="B10" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E10" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="F10" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="G10" t="s">
-        <v>254</v>
+        <v>133</v>
       </c>
       <c r="H10" t="s">
-        <v>262</v>
+        <v>284</v>
       </c>
       <c r="I10" t="s">
-        <v>270</v>
+        <v>296</v>
       </c>
       <c r="J10" t="s">
-        <v>270</v>
+        <v>296</v>
       </c>
       <c r="K10" t="s">
-        <v>280</v>
+        <v>311</v>
       </c>
       <c r="L10" t="s">
-        <v>288</v>
+        <v>323</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="B11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C11" t="s">
+        <v>227</v>
+      </c>
+      <c r="D11" t="s">
+        <v>238</v>
+      </c>
+      <c r="E11" t="s">
+        <v>250</v>
+      </c>
+      <c r="F11" t="s">
+        <v>262</v>
+      </c>
+      <c r="G11" t="s">
+        <v>273</v>
+      </c>
+      <c r="H11" t="s">
+        <v>285</v>
+      </c>
+      <c r="I11" t="s">
+        <v>297</v>
+      </c>
+      <c r="J11" t="s">
+        <v>297</v>
+      </c>
+      <c r="K11" t="s">
+        <v>312</v>
+      </c>
+      <c r="L11" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="B12" t="s">
+        <v>217</v>
+      </c>
+      <c r="C12" t="s">
+        <v>228</v>
+      </c>
+      <c r="D12" t="s">
+        <v>239</v>
+      </c>
+      <c r="E12" t="s">
+        <v>251</v>
+      </c>
+      <c r="F12" t="s">
+        <v>263</v>
+      </c>
+      <c r="G12" t="s">
+        <v>274</v>
+      </c>
+      <c r="H12" t="s">
+        <v>286</v>
+      </c>
+      <c r="I12" t="s">
+        <v>298</v>
+      </c>
+      <c r="J12" t="s">
+        <v>298</v>
+      </c>
+      <c r="K12" t="s">
+        <v>313</v>
+      </c>
+      <c r="L12" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="B13" t="s">
         <v>218</v>
       </c>
-      <c r="C11" t="s">
-        <v>225</v>
-      </c>
-      <c r="D11" t="s">
-        <v>232</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="C13" t="s">
+        <v>229</v>
+      </c>
+      <c r="D13" t="s">
         <v>240</v>
       </c>
-      <c r="F11" t="s">
-        <v>248</v>
-      </c>
-      <c r="G11" t="s">
-        <v>255</v>
-      </c>
-      <c r="H11" t="s">
-        <v>263</v>
-      </c>
-      <c r="I11" t="s">
-        <v>271</v>
-      </c>
-      <c r="J11" t="s">
-        <v>271</v>
-      </c>
-      <c r="K11" t="s">
-        <v>281</v>
-      </c>
-      <c r="L11" t="s">
+      <c r="E13" t="s">
         <v>252</v>
+      </c>
+      <c r="F13" t="s">
+        <v>264</v>
+      </c>
+      <c r="G13" t="s">
+        <v>275</v>
+      </c>
+      <c r="H13" t="s">
+        <v>287</v>
+      </c>
+      <c r="I13" t="s">
+        <v>299</v>
+      </c>
+      <c r="J13" t="s">
+        <v>299</v>
+      </c>
+      <c r="K13" t="s">
+        <v>314</v>
+      </c>
+      <c r="L13" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="B14" t="s">
+        <v>219</v>
+      </c>
+      <c r="C14" t="s">
+        <v>230</v>
+      </c>
+      <c r="D14" t="s">
+        <v>241</v>
+      </c>
+      <c r="E14" t="s">
+        <v>253</v>
+      </c>
+      <c r="F14" t="s">
+        <v>265</v>
+      </c>
+      <c r="G14" t="s">
+        <v>276</v>
+      </c>
+      <c r="H14" t="s">
+        <v>288</v>
+      </c>
+      <c r="I14" t="s">
+        <v>300</v>
+      </c>
+      <c r="J14" t="s">
+        <v>300</v>
+      </c>
+      <c r="K14" t="s">
+        <v>315</v>
+      </c>
+      <c r="L14" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="B15" t="s">
+        <v>220</v>
+      </c>
+      <c r="C15" t="s">
+        <v>231</v>
+      </c>
+      <c r="D15" t="s">
+        <v>242</v>
+      </c>
+      <c r="E15" t="s">
+        <v>254</v>
+      </c>
+      <c r="F15" t="s">
+        <v>266</v>
+      </c>
+      <c r="G15" t="s">
+        <v>277</v>
+      </c>
+      <c r="H15" t="s">
+        <v>289</v>
+      </c>
+      <c r="I15" t="s">
+        <v>301</v>
+      </c>
+      <c r="J15" t="s">
+        <v>301</v>
+      </c>
+      <c r="K15" t="s">
+        <v>316</v>
+      </c>
+      <c r="L15" t="s">
+        <v>272</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:A6"/>
-    <mergeCell ref="A7:A11"/>
+    <mergeCell ref="A2:A8"/>
+    <mergeCell ref="A9:A15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3898,7 +4188,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -4017,34 +4307,34 @@
         <v>216</v>
       </c>
       <c r="C4">
-        <v>0.67</v>
+        <v>0.674</v>
       </c>
       <c r="D4">
-        <v>0.227</v>
+        <v>0.251</v>
       </c>
       <c r="E4">
-        <v>0.622</v>
+        <v>0.62</v>
       </c>
       <c r="F4">
-        <v>0.262</v>
+        <v>0.257</v>
       </c>
       <c r="G4">
-        <v>0.681</v>
+        <v>0.725</v>
       </c>
       <c r="H4">
-        <v>0.261</v>
+        <v>0.271</v>
       </c>
       <c r="I4">
-        <v>0.707</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J4">
-        <v>0.235</v>
+        <v>0.303</v>
       </c>
       <c r="K4">
-        <v>0.63</v>
+        <v>0.604</v>
       </c>
       <c r="L4">
-        <v>0.203</v>
+        <v>0.211</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -4052,34 +4342,34 @@
         <v>217</v>
       </c>
       <c r="C5">
-        <v>0.604</v>
+        <v>0.67</v>
       </c>
       <c r="D5">
-        <v>0.213</v>
+        <v>0.227</v>
       </c>
       <c r="E5">
-        <v>0.571</v>
+        <v>0.622</v>
       </c>
       <c r="F5">
-        <v>0.212</v>
+        <v>0.262</v>
       </c>
       <c r="G5">
-        <v>0.579</v>
+        <v>0.681</v>
       </c>
       <c r="H5">
-        <v>0.212</v>
+        <v>0.261</v>
       </c>
       <c r="I5">
-        <v>0.574</v>
+        <v>0.707</v>
       </c>
       <c r="J5">
-        <v>0.216</v>
+        <v>0.235</v>
       </c>
       <c r="K5">
-        <v>0.54</v>
+        <v>0.63</v>
       </c>
       <c r="L5">
-        <v>0.219</v>
+        <v>0.203</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -4087,218 +4377,358 @@
         <v>218</v>
       </c>
       <c r="C6">
-        <v>0.592</v>
+        <v>0.604</v>
       </c>
       <c r="D6">
         <v>0.213</v>
       </c>
       <c r="E6">
-        <v>0.573</v>
+        <v>0.571</v>
       </c>
       <c r="F6">
         <v>0.212</v>
       </c>
       <c r="G6">
-        <v>0.59</v>
+        <v>0.579</v>
       </c>
       <c r="H6">
-        <v>0.203</v>
+        <v>0.212</v>
       </c>
       <c r="I6">
-        <v>0.578</v>
+        <v>0.574</v>
       </c>
       <c r="J6">
-        <v>0.213</v>
+        <v>0.216</v>
       </c>
       <c r="K6">
-        <v>0.545</v>
+        <v>0.54</v>
       </c>
       <c r="L6">
-        <v>0.218</v>
+        <v>0.219</v>
       </c>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" t="s">
-        <v>81</v>
-      </c>
       <c r="B7" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="C7">
-        <v>0.635</v>
+        <v>0.704</v>
       </c>
       <c r="D7">
-        <v>0.181</v>
+        <v>0.294</v>
       </c>
       <c r="E7">
-        <v>0.492</v>
+        <v>0.647</v>
       </c>
       <c r="F7">
-        <v>0.166</v>
+        <v>0.294</v>
       </c>
       <c r="G7">
-        <v>0.661</v>
+        <v>0.679</v>
       </c>
       <c r="H7">
-        <v>0.21</v>
+        <v>0.219</v>
       </c>
       <c r="I7">
-        <v>0.751</v>
+        <v>0.732</v>
       </c>
       <c r="J7">
-        <v>0.232</v>
+        <v>0.219</v>
       </c>
       <c r="K7">
-        <v>0.647</v>
+        <v>0.626</v>
       </c>
       <c r="L7">
-        <v>0.155</v>
+        <v>0.246</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="B8" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="C8">
-        <v>0.634</v>
+        <v>0.592</v>
       </c>
       <c r="D8">
-        <v>0.183</v>
+        <v>0.213</v>
       </c>
       <c r="E8">
-        <v>0.51</v>
+        <v>0.573</v>
       </c>
       <c r="F8">
-        <v>0.173</v>
+        <v>0.212</v>
       </c>
       <c r="G8">
-        <v>0.657</v>
+        <v>0.59</v>
       </c>
       <c r="H8">
-        <v>0.208</v>
+        <v>0.203</v>
       </c>
       <c r="I8">
-        <v>0.748</v>
+        <v>0.578</v>
       </c>
       <c r="J8">
-        <v>0.236</v>
+        <v>0.213</v>
       </c>
       <c r="K8">
-        <v>0.634</v>
+        <v>0.545</v>
       </c>
       <c r="L8">
-        <v>0.158</v>
+        <v>0.218</v>
       </c>
     </row>
     <row r="9" spans="1:12">
+      <c r="A9" t="s">
+        <v>81</v>
+      </c>
       <c r="B9" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C9">
-        <v>0.588</v>
+        <v>0.635</v>
       </c>
       <c r="D9">
-        <v>0.158</v>
+        <v>0.181</v>
       </c>
       <c r="E9">
-        <v>0.48</v>
+        <v>0.492</v>
       </c>
       <c r="F9">
-        <v>0.152</v>
+        <v>0.166</v>
       </c>
       <c r="G9">
-        <v>0.631</v>
+        <v>0.661</v>
       </c>
       <c r="H9">
-        <v>0.178</v>
+        <v>0.21</v>
       </c>
       <c r="I9">
-        <v>0.702</v>
+        <v>0.751</v>
       </c>
       <c r="J9">
-        <v>0.195</v>
+        <v>0.232</v>
       </c>
       <c r="K9">
-        <v>0.5570000000000001</v>
+        <v>0.647</v>
       </c>
       <c r="L9">
-        <v>0.133</v>
+        <v>0.155</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="B10" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C10">
-        <v>0.603</v>
+        <v>0.634</v>
       </c>
       <c r="D10">
-        <v>0.231</v>
+        <v>0.183</v>
       </c>
       <c r="E10">
-        <v>0.555</v>
+        <v>0.51</v>
       </c>
       <c r="F10">
-        <v>0.238</v>
+        <v>0.173</v>
       </c>
       <c r="G10">
-        <v>0.606</v>
+        <v>0.657</v>
       </c>
       <c r="H10">
-        <v>0.217</v>
+        <v>0.208</v>
       </c>
       <c r="I10">
-        <v>0.592</v>
+        <v>0.748</v>
       </c>
       <c r="J10">
-        <v>0.229</v>
+        <v>0.236</v>
       </c>
       <c r="K10">
-        <v>0.609</v>
+        <v>0.634</v>
       </c>
       <c r="L10">
-        <v>0.225</v>
+        <v>0.158</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="B11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C11">
+        <v>0.452</v>
+      </c>
+      <c r="D11">
+        <v>0.094</v>
+      </c>
+      <c r="E11">
+        <v>0.384</v>
+      </c>
+      <c r="F11">
+        <v>0.089</v>
+      </c>
+      <c r="G11">
+        <v>0.49</v>
+      </c>
+      <c r="H11">
+        <v>0.075</v>
+      </c>
+      <c r="I11">
+        <v>0.607</v>
+      </c>
+      <c r="J11">
+        <v>0.144</v>
+      </c>
+      <c r="K11">
+        <v>0.413</v>
+      </c>
+      <c r="L11">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="B12" t="s">
+        <v>217</v>
+      </c>
+      <c r="C12">
+        <v>0.588</v>
+      </c>
+      <c r="D12">
+        <v>0.158</v>
+      </c>
+      <c r="E12">
+        <v>0.48</v>
+      </c>
+      <c r="F12">
+        <v>0.152</v>
+      </c>
+      <c r="G12">
+        <v>0.631</v>
+      </c>
+      <c r="H12">
+        <v>0.178</v>
+      </c>
+      <c r="I12">
+        <v>0.702</v>
+      </c>
+      <c r="J12">
+        <v>0.195</v>
+      </c>
+      <c r="K12">
+        <v>0.5570000000000001</v>
+      </c>
+      <c r="L12">
+        <v>0.133</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="B13" t="s">
         <v>218</v>
       </c>
-      <c r="C11">
+      <c r="C13">
+        <v>0.603</v>
+      </c>
+      <c r="D13">
+        <v>0.231</v>
+      </c>
+      <c r="E13">
+        <v>0.555</v>
+      </c>
+      <c r="F13">
+        <v>0.238</v>
+      </c>
+      <c r="G13">
+        <v>0.606</v>
+      </c>
+      <c r="H13">
+        <v>0.217</v>
+      </c>
+      <c r="I13">
+        <v>0.592</v>
+      </c>
+      <c r="J13">
+        <v>0.229</v>
+      </c>
+      <c r="K13">
+        <v>0.609</v>
+      </c>
+      <c r="L13">
+        <v>0.225</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="B14" t="s">
+        <v>219</v>
+      </c>
+      <c r="C14">
+        <v>0.677</v>
+      </c>
+      <c r="D14">
+        <v>0.238</v>
+      </c>
+      <c r="E14">
+        <v>0.571</v>
+      </c>
+      <c r="F14">
+        <v>0.233</v>
+      </c>
+      <c r="G14">
+        <v>0.6860000000000001</v>
+      </c>
+      <c r="H14">
+        <v>0.236</v>
+      </c>
+      <c r="I14">
+        <v>0.71</v>
+      </c>
+      <c r="J14">
+        <v>0.191</v>
+      </c>
+      <c r="K14">
+        <v>0.668</v>
+      </c>
+      <c r="L14">
+        <v>0.201</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="B15" t="s">
+        <v>220</v>
+      </c>
+      <c r="C15">
         <v>0.608</v>
       </c>
-      <c r="D11">
+      <c r="D15">
         <v>0.226</v>
       </c>
-      <c r="E11">
+      <c r="E15">
         <v>0.5570000000000001</v>
       </c>
-      <c r="F11">
+      <c r="F15">
         <v>0.234</v>
       </c>
-      <c r="G11">
+      <c r="G15">
         <v>0.598</v>
       </c>
-      <c r="H11">
+      <c r="H15">
         <v>0.232</v>
       </c>
-      <c r="I11">
+      <c r="I15">
         <v>0.601</v>
       </c>
-      <c r="J11">
+      <c r="J15">
         <v>0.238</v>
       </c>
-      <c r="K11">
+      <c r="K15">
         <v>0.609</v>
       </c>
-      <c r="L11">
+      <c r="L15">
         <v>0.232</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:A6"/>
-    <mergeCell ref="A7:A11"/>
+    <mergeCell ref="A2:A8"/>
+    <mergeCell ref="A9:A15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4306,7 +4736,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -4317,22 +4747,22 @@
         <v>213</v>
       </c>
       <c r="D1" t="s">
-        <v>289</v>
+        <v>328</v>
       </c>
       <c r="E1" t="s">
-        <v>290</v>
+        <v>329</v>
       </c>
       <c r="F1" t="s">
-        <v>291</v>
+        <v>330</v>
       </c>
       <c r="G1" t="s">
-        <v>292</v>
+        <v>331</v>
       </c>
       <c r="H1" t="s">
-        <v>293</v>
+        <v>332</v>
       </c>
       <c r="I1" t="s">
-        <v>294</v>
+        <v>333</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -4343,13 +4773,13 @@
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>295</v>
+        <v>334</v>
       </c>
       <c r="D2">
         <v>0.011</v>
       </c>
       <c r="E2" t="s">
-        <v>299</v>
+        <v>340</v>
       </c>
       <c r="F2">
         <v>0.644</v>
@@ -4358,7 +4788,7 @@
         <v>-0.004</v>
       </c>
       <c r="H2" t="s">
-        <v>307</v>
+        <v>352</v>
       </c>
       <c r="I2">
         <v>0.158</v>
@@ -4372,25 +4802,25 @@
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>296</v>
+        <v>335</v>
       </c>
       <c r="D3">
-        <v>-0.08500000000000001</v>
+        <v>-0.003</v>
       </c>
       <c r="E3" t="s">
-        <v>300</v>
+        <v>341</v>
       </c>
       <c r="F3">
-        <v>0.12</v>
+        <v>0.844</v>
       </c>
       <c r="G3">
-        <v>-0.012</v>
+        <v>-0.008</v>
       </c>
       <c r="H3" t="s">
-        <v>308</v>
+        <v>353</v>
       </c>
       <c r="I3">
-        <v>0.074</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -4401,25 +4831,25 @@
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>297</v>
+        <v>336</v>
       </c>
       <c r="D4">
-        <v>-0.098</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="E4" t="s">
-        <v>301</v>
+        <v>342</v>
       </c>
       <c r="F4">
-        <v>0.126</v>
+        <v>0.12</v>
       </c>
       <c r="G4">
-        <v>-0.052</v>
+        <v>-0.012</v>
       </c>
       <c r="H4" t="s">
-        <v>309</v>
+        <v>354</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>0.074</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -4430,22 +4860,22 @@
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>298</v>
+        <v>337</v>
       </c>
       <c r="D5">
-        <v>-0.07000000000000001</v>
+        <v>-0.098</v>
       </c>
       <c r="E5" t="s">
-        <v>302</v>
+        <v>343</v>
       </c>
       <c r="F5">
-        <v>0.372</v>
+        <v>0.126</v>
       </c>
       <c r="G5">
-        <v>-0.058</v>
+        <v>-0.052</v>
       </c>
       <c r="H5" t="s">
-        <v>310</v>
+        <v>355</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4456,28 +4886,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>295</v>
+        <v>338</v>
       </c>
       <c r="D6">
-        <v>-0.025</v>
+        <v>-0.074</v>
       </c>
       <c r="E6" t="s">
-        <v>303</v>
+        <v>344</v>
       </c>
       <c r="F6">
-        <v>0.254</v>
+        <v>0.036</v>
       </c>
       <c r="G6">
+        <v>-0.014</v>
+      </c>
+      <c r="H6" t="s">
+        <v>356</v>
+      </c>
+      <c r="I6">
         <v>0</v>
-      </c>
-      <c r="H6" t="s">
-        <v>311</v>
-      </c>
-      <c r="I6">
-        <v>0.986</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -4485,28 +4915,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>296</v>
+        <v>339</v>
       </c>
       <c r="D7">
-        <v>-0.035</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E7" t="s">
-        <v>304</v>
+        <v>345</v>
       </c>
       <c r="F7">
-        <v>0.268</v>
+        <v>0.372</v>
       </c>
       <c r="G7">
-        <v>-0.008</v>
+        <v>-0.058</v>
       </c>
       <c r="H7" t="s">
-        <v>312</v>
+        <v>357</v>
       </c>
       <c r="I7">
-        <v>0.066</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -4517,25 +4947,25 @@
         <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>297</v>
+        <v>334</v>
       </c>
       <c r="D8">
-        <v>-0.067</v>
+        <v>-0.025</v>
       </c>
       <c r="E8" t="s">
-        <v>305</v>
+        <v>346</v>
       </c>
       <c r="F8">
-        <v>0.344</v>
+        <v>0.254</v>
       </c>
       <c r="G8">
-        <v>-0.053</v>
+        <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>313</v>
+        <v>358</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>0.986</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -4546,24 +4976,140 @@
         <v>81</v>
       </c>
       <c r="C9" t="s">
-        <v>298</v>
+        <v>335</v>
       </c>
       <c r="D9">
+        <v>-0.014</v>
+      </c>
+      <c r="E9" t="s">
+        <v>347</v>
+      </c>
+      <c r="F9">
+        <v>0.758</v>
+      </c>
+      <c r="G9">
+        <v>-0.031</v>
+      </c>
+      <c r="H9" t="s">
+        <v>359</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C10" t="s">
+        <v>336</v>
+      </c>
+      <c r="D10">
+        <v>-0.035</v>
+      </c>
+      <c r="E10" t="s">
+        <v>348</v>
+      </c>
+      <c r="F10">
+        <v>0.268</v>
+      </c>
+      <c r="G10">
+        <v>-0.008</v>
+      </c>
+      <c r="H10" t="s">
+        <v>360</v>
+      </c>
+      <c r="I10">
+        <v>0.066</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>81</v>
+      </c>
+      <c r="C11" t="s">
+        <v>337</v>
+      </c>
+      <c r="D11">
+        <v>-0.067</v>
+      </c>
+      <c r="E11" t="s">
+        <v>349</v>
+      </c>
+      <c r="F11">
+        <v>0.344</v>
+      </c>
+      <c r="G11">
+        <v>-0.053</v>
+      </c>
+      <c r="H11" t="s">
+        <v>361</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>81</v>
+      </c>
+      <c r="C12" t="s">
+        <v>338</v>
+      </c>
+      <c r="D12">
+        <v>-0.075</v>
+      </c>
+      <c r="E12" t="s">
+        <v>350</v>
+      </c>
+      <c r="F12">
+        <v>0.092</v>
+      </c>
+      <c r="G12">
+        <v>-0</v>
+      </c>
+      <c r="H12" t="s">
+        <v>358</v>
+      </c>
+      <c r="I12">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" t="s">
+        <v>339</v>
+      </c>
+      <c r="D13">
         <v>-0.042</v>
       </c>
-      <c r="E9" t="s">
-        <v>306</v>
-      </c>
-      <c r="F9">
+      <c r="E13" t="s">
+        <v>351</v>
+      </c>
+      <c r="F13">
         <v>0.58</v>
       </c>
-      <c r="G9">
+      <c r="G13">
         <v>-0.059</v>
       </c>
-      <c r="H9" t="s">
-        <v>314</v>
-      </c>
-      <c r="I9">
+      <c r="H13" t="s">
+        <v>362</v>
+      </c>
+      <c r="I13">
         <v>0</v>
       </c>
     </row>
@@ -4579,13 +5125,13 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" t="s">
-        <v>315</v>
+        <v>363</v>
       </c>
       <c r="C1" t="s">
-        <v>316</v>
+        <v>364</v>
       </c>
       <c r="D1" t="s">
-        <v>317</v>
+        <v>365</v>
       </c>
       <c r="E1" t="s">
         <v>194</v>
@@ -4594,10 +5140,10 @@
         <v>213</v>
       </c>
       <c r="G1" t="s">
-        <v>318</v>
+        <v>366</v>
       </c>
       <c r="H1" t="s">
-        <v>319</v>
+        <v>367</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -4611,19 +5157,19 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>320</v>
+        <v>368</v>
       </c>
       <c r="E2" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F2" t="s">
-        <v>296</v>
+        <v>338</v>
       </c>
       <c r="G2">
-        <v>0.719</v>
+        <v>0.731</v>
       </c>
       <c r="H2">
-        <v>0.157</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -4637,7 +5183,7 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>321</v>
+        <v>369</v>
       </c>
       <c r="E3" t="s">
         <v>81</v>
@@ -4663,19 +5209,19 @@
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>320</v>
+        <v>368</v>
       </c>
       <c r="E4" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F4" t="s">
-        <v>296</v>
+        <v>338</v>
       </c>
       <c r="G4">
         <v>0.725</v>
       </c>
       <c r="H4">
-        <v>0.242</v>
+        <v>0.129</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -4689,7 +5235,7 @@
         <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>321</v>
+        <v>369</v>
       </c>
       <c r="E5" t="s">
         <v>75</v>
@@ -4715,19 +5261,19 @@
         <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>320</v>
+        <v>368</v>
       </c>
       <c r="E6" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F6" t="s">
-        <v>296</v>
+        <v>338</v>
       </c>
       <c r="G6">
-        <v>0.718</v>
+        <v>0.727</v>
       </c>
       <c r="H6">
-        <v>0.133</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -4741,7 +5287,7 @@
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>321</v>
+        <v>369</v>
       </c>
       <c r="E7" t="s">
         <v>81</v>
@@ -4767,19 +5313,19 @@
         <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>320</v>
+        <v>368</v>
       </c>
       <c r="E8" t="s">
         <v>75</v>
       </c>
       <c r="F8" t="s">
-        <v>296</v>
+        <v>338</v>
       </c>
       <c r="G8">
-        <v>0.74</v>
+        <v>0.732</v>
       </c>
       <c r="H8">
-        <v>0.167</v>
+        <v>0.091</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -4793,7 +5339,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>321</v>
+        <v>369</v>
       </c>
       <c r="E9" t="s">
         <v>75</v>
@@ -4819,13 +5365,13 @@
         <v>5</v>
       </c>
       <c r="D10" t="s">
-        <v>320</v>
+        <v>368</v>
       </c>
       <c r="E10" t="s">
         <v>75</v>
       </c>
       <c r="F10" t="s">
-        <v>296</v>
+        <v>336</v>
       </c>
       <c r="G10">
         <v>0.716</v>
@@ -4845,7 +5391,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="s">
-        <v>321</v>
+        <v>369</v>
       </c>
       <c r="E11" t="s">
         <v>75</v>
@@ -4871,13 +5417,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>320</v>
+        <v>368</v>
       </c>
       <c r="E12" t="s">
         <v>75</v>
       </c>
       <c r="F12" t="s">
-        <v>296</v>
+        <v>336</v>
       </c>
       <c r="G12">
         <v>0.713</v>
@@ -4897,7 +5443,7 @@
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>321</v>
+        <v>369</v>
       </c>
       <c r="E13" t="s">
         <v>75</v>
@@ -4923,13 +5469,13 @@
         <v>2</v>
       </c>
       <c r="D14" t="s">
-        <v>320</v>
+        <v>368</v>
       </c>
       <c r="E14" t="s">
         <v>75</v>
       </c>
       <c r="F14" t="s">
-        <v>296</v>
+        <v>336</v>
       </c>
       <c r="G14">
         <v>0.729</v>
@@ -4949,7 +5495,7 @@
         <v>2</v>
       </c>
       <c r="D15" t="s">
-        <v>321</v>
+        <v>369</v>
       </c>
       <c r="E15" t="s">
         <v>75</v>
@@ -4975,19 +5521,19 @@
         <v>3</v>
       </c>
       <c r="D16" t="s">
-        <v>320</v>
+        <v>368</v>
       </c>
       <c r="E16" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F16" t="s">
-        <v>296</v>
+        <v>338</v>
       </c>
       <c r="G16">
-        <v>0.725</v>
+        <v>0.718</v>
       </c>
       <c r="H16">
-        <v>0.129</v>
+        <v>0.08599999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -5001,7 +5547,7 @@
         <v>3</v>
       </c>
       <c r="D17" t="s">
-        <v>321</v>
+        <v>369</v>
       </c>
       <c r="E17" t="s">
         <v>75</v>
@@ -5027,19 +5573,19 @@
         <v>4</v>
       </c>
       <c r="D18" t="s">
-        <v>320</v>
+        <v>368</v>
       </c>
       <c r="E18" t="s">
         <v>81</v>
       </c>
       <c r="F18" t="s">
-        <v>296</v>
+        <v>338</v>
       </c>
       <c r="G18">
-        <v>0.722</v>
+        <v>0.721</v>
       </c>
       <c r="H18">
-        <v>0.218</v>
+        <v>0.149</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -5053,7 +5599,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="s">
-        <v>321</v>
+        <v>369</v>
       </c>
       <c r="E19" t="s">
         <v>81</v>
@@ -5079,19 +5625,19 @@
         <v>5</v>
       </c>
       <c r="D20" t="s">
-        <v>320</v>
+        <v>368</v>
       </c>
       <c r="E20" t="s">
         <v>75</v>
       </c>
       <c r="F20" t="s">
-        <v>296</v>
+        <v>338</v>
       </c>
       <c r="G20">
-        <v>0.72</v>
+        <v>0.731</v>
       </c>
       <c r="H20">
-        <v>0.106</v>
+        <v>0.101</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -5105,7 +5651,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="s">
-        <v>321</v>
+        <v>369</v>
       </c>
       <c r="E21" t="s">
         <v>75</v>
@@ -5132,7 +5678,7 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>317</v>
+        <v>365</v>
       </c>
       <c r="B1" t="s">
         <v>69</v>
@@ -5155,48 +5701,48 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>320</v>
+        <v>368</v>
       </c>
       <c r="B2" t="s">
-        <v>82</v>
+        <v>370</v>
       </c>
       <c r="C2" t="s">
-        <v>323</v>
+        <v>372</v>
       </c>
       <c r="D2" t="s">
-        <v>325</v>
+        <v>374</v>
       </c>
       <c r="E2" t="s">
-        <v>327</v>
+        <v>375</v>
       </c>
       <c r="F2" t="s">
-        <v>327</v>
+        <v>375</v>
       </c>
       <c r="G2" t="s">
-        <v>329</v>
+        <v>377</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>321</v>
+        <v>369</v>
       </c>
       <c r="B3" t="s">
-        <v>322</v>
+        <v>371</v>
       </c>
       <c r="C3" t="s">
-        <v>324</v>
+        <v>373</v>
       </c>
       <c r="D3" t="s">
-        <v>326</v>
+        <v>247</v>
       </c>
       <c r="E3" t="s">
-        <v>328</v>
+        <v>376</v>
       </c>
       <c r="F3" t="s">
-        <v>328</v>
+        <v>376</v>
       </c>
       <c r="G3" t="s">
-        <v>330</v>
+        <v>378</v>
       </c>
     </row>
   </sheetData>
@@ -5206,7 +5752,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -5217,7 +5763,7 @@
         <v>213</v>
       </c>
       <c r="D1" t="s">
-        <v>331</v>
+        <v>379</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -5228,10 +5774,10 @@
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>296</v>
+        <v>336</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -5239,13 +5785,27 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" t="s">
+        <v>338</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
         <v>81</v>
       </c>
-      <c r="C3" t="s">
-        <v>296</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
+      <c r="C4" t="s">
+        <v>338</v>
+      </c>
+      <c r="D4">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5255,7 +5815,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -5272,7 +5832,7 @@
         <v>127</v>
       </c>
       <c r="E1" t="s">
-        <v>332</v>
+        <v>380</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -5311,13 +5871,13 @@
         <v>216</v>
       </c>
       <c r="C4">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="D4">
-        <v>0.092</v>
+        <v>0.211</v>
       </c>
       <c r="E4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -5325,10 +5885,10 @@
         <v>217</v>
       </c>
       <c r="C5">
-        <v>0.6830000000000001</v>
+        <v>0.72</v>
       </c>
       <c r="D5">
-        <v>0.079</v>
+        <v>0.092</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
@@ -5339,27 +5899,24 @@
         <v>218</v>
       </c>
       <c r="C6">
-        <v>0.6850000000000001</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="D6">
-        <v>0.098</v>
+        <v>0.079</v>
       </c>
       <c r="E6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" t="s">
-        <v>81</v>
-      </c>
       <c r="B7" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="C7">
-        <v>0.736</v>
+        <v>0.724</v>
       </c>
       <c r="D7">
-        <v>0.259</v>
+        <v>0.116</v>
       </c>
       <c r="E7" t="b">
         <v>1</v>
@@ -5367,41 +5924,44 @@
     </row>
     <row r="8" spans="1:5">
       <c r="B8" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="C8">
-        <v>0.734</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="D8">
-        <v>0.238</v>
+        <v>0.098</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>81</v>
+      </c>
       <c r="B9" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C9">
-        <v>0.729</v>
+        <v>0.736</v>
       </c>
       <c r="D9">
-        <v>0.222</v>
+        <v>0.259</v>
       </c>
       <c r="E9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="B10" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C10">
-        <v>0.6830000000000001</v>
+        <v>0.734</v>
       </c>
       <c r="D10">
-        <v>0.095</v>
+        <v>0.238</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -5409,22 +5969,78 @@
     </row>
     <row r="11" spans="1:5">
       <c r="B11" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C11">
-        <v>0.6820000000000001</v>
+        <v>0.704</v>
       </c>
       <c r="D11">
-        <v>0.116</v>
+        <v>0.23</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
       </c>
     </row>
+    <row r="12" spans="1:5">
+      <c r="B12" t="s">
+        <v>217</v>
+      </c>
+      <c r="C12">
+        <v>0.729</v>
+      </c>
+      <c r="D12">
+        <v>0.222</v>
+      </c>
+      <c r="E12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="B13" t="s">
+        <v>218</v>
+      </c>
+      <c r="C13">
+        <v>0.6830000000000001</v>
+      </c>
+      <c r="D13">
+        <v>0.095</v>
+      </c>
+      <c r="E13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="B14" t="s">
+        <v>219</v>
+      </c>
+      <c r="C14">
+        <v>0.731</v>
+      </c>
+      <c r="D14">
+        <v>0.143</v>
+      </c>
+      <c r="E14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="B15" t="s">
+        <v>220</v>
+      </c>
+      <c r="C15">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="D15">
+        <v>0.116</v>
+      </c>
+      <c r="E15" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:A6"/>
-    <mergeCell ref="A7:A11"/>
+    <mergeCell ref="A2:A8"/>
+    <mergeCell ref="A9:A15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5432,476 +6048,418 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:7">
       <c r="B1" t="s">
-        <v>194</v>
+        <v>20</v>
       </c>
       <c r="C1" t="s">
-        <v>213</v>
+        <v>21</v>
       </c>
       <c r="D1" t="s">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="E1" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="F1" t="s">
-        <v>71</v>
+        <v>24</v>
       </c>
       <c r="G1" t="s">
-        <v>73</v>
-      </c>
-      <c r="H1" t="s">
-        <v>126</v>
-      </c>
-      <c r="I1" t="s">
-        <v>127</v>
-      </c>
-      <c r="J1" t="s">
-        <v>169</v>
-      </c>
-      <c r="K1" t="s">
-        <v>174</v>
-      </c>
-      <c r="L1" t="s">
-        <v>179</v>
-      </c>
-      <c r="M1" t="s">
-        <v>184</v>
-      </c>
-      <c r="N1" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2">
+        <v>0.4474000036716461</v>
+      </c>
+      <c r="C2">
+        <v>0.4706999957561493</v>
+      </c>
+      <c r="D2">
+        <v>0.4632999897003174</v>
+      </c>
+      <c r="E2">
+        <v>0.5756999850273132</v>
+      </c>
+      <c r="F2">
+        <v>0.4815999865531921</v>
+      </c>
+      <c r="G2">
+        <v>0.5005999803543091</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3">
+        <v>0.3628999888896942</v>
+      </c>
+      <c r="C3">
+        <v>0.3416999876499176</v>
+      </c>
+      <c r="D3">
+        <v>0.440200001001358</v>
+      </c>
+      <c r="E3">
+        <v>0.4465999901294708</v>
+      </c>
+      <c r="F3">
+        <v>0.3731000125408173</v>
+      </c>
+      <c r="G3">
+        <v>0.4066999852657318</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4">
+        <v>0.2381000071763992</v>
+      </c>
+      <c r="C4">
+        <v>0.2282000035047531</v>
+      </c>
+      <c r="D4">
+        <v>0.2657999992370605</v>
+      </c>
+      <c r="E4">
+        <v>0.2300000041723251</v>
+      </c>
+      <c r="F4">
+        <v>0.2348999977111816</v>
+      </c>
+      <c r="G4">
+        <v>0.2398000061511993</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5">
+        <v>0.2181999981403351</v>
+      </c>
+      <c r="C5">
+        <v>0.225600004196167</v>
+      </c>
+      <c r="D5">
+        <v>0.2599999904632568</v>
+      </c>
+      <c r="E5">
+        <v>0.2398999929428101</v>
+      </c>
+      <c r="F5">
+        <v>0.2260999977588654</v>
+      </c>
+      <c r="G5">
+        <v>0.2364999949932098</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6">
+        <v>0.1859000027179718</v>
+      </c>
+      <c r="C6">
+        <v>0.1787000000476837</v>
+      </c>
+      <c r="D6">
+        <v>0.1754000037908554</v>
+      </c>
+      <c r="E6">
+        <v>0.1729000061750412</v>
+      </c>
+      <c r="F6">
+        <v>0.1898999959230423</v>
+      </c>
+      <c r="G6">
+        <v>0.1782000064849854</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B7">
+        <v>0.1831000000238419</v>
+      </c>
+      <c r="C7">
+        <v>0.1697999984025955</v>
+      </c>
+      <c r="D7">
+        <v>0.160300001502037</v>
+      </c>
+      <c r="E7">
+        <v>0.1678999960422516</v>
+      </c>
+      <c r="F7">
+        <v>0.1676999926567078</v>
+      </c>
+      <c r="G7">
+        <v>0.1701000034809113</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B8">
+        <v>0.120899997651577</v>
+      </c>
+      <c r="C8">
+        <v>0.1275999993085861</v>
+      </c>
+      <c r="D8">
+        <v>0.1372999995946884</v>
+      </c>
+      <c r="E8">
+        <v>0.1174999997019768</v>
+      </c>
+      <c r="F8">
+        <v>0.1319999992847443</v>
+      </c>
+      <c r="G8">
+        <v>0.1248999983072281</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9">
+        <v>0.1220000013709068</v>
+      </c>
+      <c r="C9">
+        <v>0.120399996638298</v>
+      </c>
+      <c r="D9">
+        <v>0.1326999962329865</v>
+      </c>
+      <c r="E9">
+        <v>0.1234999969601631</v>
+      </c>
+      <c r="F9">
+        <v>0.1204999983310699</v>
+      </c>
+      <c r="G9">
+        <v>0.124600000679493</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>66</v>
+      </c>
+      <c r="B10">
+        <v>0.1085999980568886</v>
+      </c>
+      <c r="C10">
+        <v>0.1260000020265579</v>
+      </c>
+      <c r="D10">
+        <v>0.1324999928474426</v>
+      </c>
+      <c r="E10">
+        <v>0.121799997985363</v>
+      </c>
+      <c r="F10">
+        <v>0.1234999969601631</v>
+      </c>
+      <c r="G10">
+        <v>0.1216999962925911</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11">
+        <v>0.1076000034809113</v>
+      </c>
+      <c r="C11">
+        <v>0.13230000436306</v>
+      </c>
+      <c r="D11">
+        <v>0.122699998319149</v>
+      </c>
+      <c r="E11">
+        <v>0.1036000028252602</v>
+      </c>
+      <c r="F11">
+        <v>0.09269999712705612</v>
+      </c>
+      <c r="G11">
+        <v>0.1123000010848045</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12">
+        <v>0.08900000154972076</v>
+      </c>
+      <c r="C12">
+        <v>0.08179999887943268</v>
+      </c>
+      <c r="D12">
+        <v>0.09409999847412109</v>
+      </c>
+      <c r="E12">
+        <v>0.0917000025510788</v>
+      </c>
+      <c r="F12">
+        <v>0.1023000031709671</v>
+      </c>
+      <c r="G12">
+        <v>0.09070000052452087</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13">
+        <v>0.09200000017881393</v>
+      </c>
+      <c r="C13">
+        <v>0.09049999713897705</v>
+      </c>
+      <c r="D13">
+        <v>0.08579999953508377</v>
+      </c>
+      <c r="E13">
+        <v>0.09149999916553497</v>
+      </c>
+      <c r="F13">
+        <v>0.09290000051259995</v>
+      </c>
+      <c r="G13">
+        <v>0.09030000120401382</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14">
+        <v>0.06840000301599503</v>
+      </c>
+      <c r="C14">
+        <v>0.06859999895095825</v>
+      </c>
+      <c r="D14">
+        <v>0.08950000256299973</v>
+      </c>
+      <c r="E14">
+        <v>0.07209999859333038</v>
+      </c>
+      <c r="F14">
+        <v>0.07800000160932541</v>
+      </c>
+      <c r="G14">
+        <v>0.07490000128746033</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15">
+        <v>0.06210000067949295</v>
+      </c>
+      <c r="C15">
+        <v>0.06949999928474426</v>
+      </c>
+      <c r="D15">
+        <v>0.07590000331401825</v>
+      </c>
+      <c r="E15">
+        <v>0.06060000136494637</v>
+      </c>
+      <c r="F15">
+        <v>0.06830000132322311</v>
+      </c>
+      <c r="G15">
+        <v>0.06599999964237213</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16">
+        <v>0.05389999970793724</v>
+      </c>
+      <c r="C16">
+        <v>0.05770000070333481</v>
+      </c>
+      <c r="D16">
+        <v>0.05620000138878822</v>
+      </c>
+      <c r="E16">
+        <v>0.05490000173449516</v>
+      </c>
+      <c r="F16">
+        <v>0.05510000139474869</v>
+      </c>
+      <c r="G16">
+        <v>0.05539999902248383</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>67</v>
+      </c>
+      <c r="B17">
+        <v>0.02950000017881393</v>
+      </c>
+      <c r="C17">
+        <v>0.02649999968707561</v>
+      </c>
+      <c r="D17">
+        <v>0.02879999950528145</v>
+      </c>
+      <c r="E17">
+        <v>0.02879999950528145</v>
+      </c>
+      <c r="F17">
+        <v>0.0272000003606081</v>
+      </c>
+      <c r="G17">
+        <v>0.02859999984502792</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C2" t="s">
-        <v>214</v>
-      </c>
-      <c r="D2">
-        <v>0.784</v>
-      </c>
-      <c r="E2">
-        <v>0.749</v>
-      </c>
-      <c r="F2">
-        <v>0.696</v>
-      </c>
-      <c r="G2">
-        <v>0.8070000000000001</v>
-      </c>
-      <c r="H2">
-        <v>0.159</v>
-      </c>
-      <c r="I2">
-        <v>0.159</v>
-      </c>
-      <c r="J2">
-        <v>0.674</v>
-      </c>
-      <c r="K2">
-        <v>0.661</v>
-      </c>
-      <c r="L2">
-        <v>0.676</v>
-      </c>
-      <c r="M2">
-        <v>0.745</v>
-      </c>
-      <c r="N2">
-        <v>0.586</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C3" t="s">
-        <v>295</v>
-      </c>
-      <c r="D3">
-        <v>0.785</v>
-      </c>
-      <c r="E3">
-        <v>0.748</v>
-      </c>
-      <c r="F3">
-        <v>0.694</v>
-      </c>
-      <c r="G3">
-        <v>0.806</v>
-      </c>
-      <c r="H3">
-        <v>0.225</v>
-      </c>
-      <c r="I3">
-        <v>0.225</v>
-      </c>
-      <c r="J3">
-        <v>0.669</v>
-      </c>
-      <c r="K3">
-        <v>0.694</v>
-      </c>
-      <c r="L3">
-        <v>0.676</v>
-      </c>
-      <c r="M3">
-        <v>0.742</v>
-      </c>
-      <c r="N3">
-        <v>0.517</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>75</v>
-      </c>
-      <c r="C4" t="s">
-        <v>296</v>
-      </c>
-      <c r="D4">
-        <v>0.778</v>
-      </c>
-      <c r="E4">
-        <v>0.73</v>
-      </c>
-      <c r="F4">
-        <v>0.66</v>
-      </c>
-      <c r="G4">
-        <v>0.74</v>
-      </c>
-      <c r="H4">
-        <v>0.08599999999999999</v>
-      </c>
-      <c r="I4">
-        <v>0.08599999999999999</v>
-      </c>
-      <c r="J4">
-        <v>0.661</v>
-      </c>
-      <c r="K4">
-        <v>0.661</v>
-      </c>
-      <c r="L4">
-        <v>0.653</v>
-      </c>
-      <c r="M4">
-        <v>0.672</v>
-      </c>
-      <c r="N4">
-        <v>0.586</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C5" t="s">
-        <v>297</v>
-      </c>
-      <c r="D5">
-        <v>0.726</v>
-      </c>
-      <c r="E5">
-        <v>0.698</v>
-      </c>
-      <c r="F5">
-        <v>0.656</v>
-      </c>
-      <c r="H5">
-        <v>0.104</v>
-      </c>
-      <c r="I5">
-        <v>0.104</v>
-      </c>
-      <c r="J5">
-        <v>0.669</v>
-      </c>
-      <c r="K5">
-        <v>0.71</v>
-      </c>
-      <c r="L5">
-        <v>0.62</v>
-      </c>
-      <c r="M5">
-        <v>0.653</v>
-      </c>
-      <c r="N5">
-        <v>0.724</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C6" t="s">
-        <v>298</v>
-      </c>
-      <c r="D6">
-        <v>0.725</v>
-      </c>
-      <c r="E6">
-        <v>0.7</v>
-      </c>
-      <c r="F6">
-        <v>0.663</v>
-      </c>
-      <c r="H6">
-        <v>0.124</v>
-      </c>
-      <c r="I6">
-        <v>0.124</v>
-      </c>
-      <c r="J6">
-        <v>0.678</v>
-      </c>
-      <c r="K6">
-        <v>0.71</v>
-      </c>
-      <c r="L6">
-        <v>0.634</v>
-      </c>
-      <c r="M6">
-        <v>0.653</v>
-      </c>
-      <c r="N6">
-        <v>0.759</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C7" t="s">
-        <v>214</v>
-      </c>
-      <c r="D7">
-        <v>0.791</v>
-      </c>
-      <c r="E7">
-        <v>0.74</v>
-      </c>
-      <c r="F7">
-        <v>0.666</v>
-      </c>
-      <c r="G7">
-        <v>0.8139999999999999</v>
-      </c>
-      <c r="H7">
-        <v>0.199</v>
-      </c>
-      <c r="I7">
-        <v>0.199</v>
-      </c>
-      <c r="J7">
-        <v>0.661</v>
-      </c>
-      <c r="K7">
-        <v>0.629</v>
-      </c>
-      <c r="L7">
-        <v>0.63</v>
-      </c>
-      <c r="M7">
-        <v>0.717</v>
-      </c>
-      <c r="N7">
-        <v>0.517</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>81</v>
-      </c>
-      <c r="C8" t="s">
-        <v>295</v>
-      </c>
-      <c r="D8">
-        <v>0.786</v>
-      </c>
-      <c r="E8">
-        <v>0.735</v>
-      </c>
-      <c r="F8">
-        <v>0.66</v>
-      </c>
-      <c r="G8">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="H8">
-        <v>0.206</v>
-      </c>
-      <c r="I8">
-        <v>0.206</v>
-      </c>
-      <c r="J8">
-        <v>0.649</v>
-      </c>
-      <c r="K8">
-        <v>0.629</v>
-      </c>
-      <c r="L8">
-        <v>0.611</v>
-      </c>
-      <c r="M8">
-        <v>0.723</v>
-      </c>
-      <c r="N8">
-        <v>0.517</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>81</v>
-      </c>
-      <c r="C9" t="s">
-        <v>296</v>
-      </c>
-      <c r="D9">
-        <v>0.8090000000000001</v>
-      </c>
-      <c r="E9">
-        <v>0.736</v>
-      </c>
-      <c r="F9">
-        <v>0.627</v>
-      </c>
-      <c r="G9">
-        <v>0.746</v>
-      </c>
-      <c r="H9">
-        <v>0.227</v>
-      </c>
-      <c r="I9">
-        <v>0.227</v>
-      </c>
-      <c r="J9">
-        <v>0.624</v>
-      </c>
-      <c r="K9">
-        <v>0.597</v>
-      </c>
-      <c r="L9">
-        <v>0.593</v>
-      </c>
-      <c r="M9">
-        <v>0.675</v>
-      </c>
-      <c r="N9">
-        <v>0.448</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>81</v>
-      </c>
-      <c r="C10" t="s">
-        <v>297</v>
-      </c>
-      <c r="D10">
-        <v>0.602</v>
-      </c>
-      <c r="E10">
-        <v>0.6830000000000001</v>
-      </c>
-      <c r="F10">
-        <v>0.803</v>
-      </c>
-      <c r="H10">
-        <v>0.204</v>
-      </c>
-      <c r="I10">
-        <v>0.204</v>
-      </c>
-      <c r="J10">
-        <v>0.8139999999999999</v>
-      </c>
-      <c r="K10">
-        <v>0.823</v>
-      </c>
-      <c r="L10">
-        <v>0.824</v>
-      </c>
-      <c r="M10">
-        <v>0.761</v>
-      </c>
-      <c r="N10">
-        <v>0.966</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>81</v>
-      </c>
-      <c r="C11" t="s">
-        <v>298</v>
-      </c>
-      <c r="D11">
-        <v>0.648</v>
-      </c>
-      <c r="E11">
-        <v>0.699</v>
-      </c>
-      <c r="F11">
-        <v>0.775</v>
-      </c>
-      <c r="H11">
-        <v>0.199</v>
-      </c>
-      <c r="I11">
-        <v>0.199</v>
-      </c>
-      <c r="J11">
-        <v>0.8179999999999999</v>
-      </c>
-      <c r="K11">
-        <v>0.774</v>
-      </c>
-      <c r="L11">
-        <v>0.769</v>
-      </c>
-      <c r="M11">
-        <v>0.732</v>
-      </c>
-      <c r="N11">
-        <v>0.931</v>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5911,418 +6469,105 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
       <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D1" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
         <v>20</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B2">
+        <v>25</v>
+      </c>
+      <c r="C2">
+        <v>3.2</v>
+      </c>
+      <c r="D2">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
         <v>21</v>
       </c>
-      <c r="D1" t="s">
+      <c r="B3">
+        <v>25</v>
+      </c>
+      <c r="C3">
+        <v>3.08</v>
+      </c>
+      <c r="D3">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
         <v>22</v>
       </c>
-      <c r="E1" t="s">
+      <c r="B4">
+        <v>25</v>
+      </c>
+      <c r="C4">
+        <v>3.04</v>
+      </c>
+      <c r="D4">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
         <v>23</v>
       </c>
-      <c r="F1" t="s">
+      <c r="B5">
+        <v>25</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
         <v>24</v>
       </c>
-      <c r="G1" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B2">
-        <v>0.4474000036716461</v>
-      </c>
-      <c r="C2">
-        <v>0.4706999957561493</v>
-      </c>
-      <c r="D2">
-        <v>0.4632999897003174</v>
-      </c>
-      <c r="E2">
-        <v>0.5756999850273132</v>
-      </c>
-      <c r="F2">
-        <v>0.4815999865531921</v>
-      </c>
-      <c r="G2">
-        <v>0.5005999803543091</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B3">
-        <v>0.3628999888896942</v>
-      </c>
-      <c r="C3">
-        <v>0.3416999876499176</v>
-      </c>
-      <c r="D3">
-        <v>0.440200001001358</v>
-      </c>
-      <c r="E3">
-        <v>0.4465999901294708</v>
-      </c>
-      <c r="F3">
-        <v>0.3731000125408173</v>
-      </c>
-      <c r="G3">
-        <v>0.4066999852657318</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B4">
-        <v>0.2381000071763992</v>
-      </c>
-      <c r="C4">
-        <v>0.2282000035047531</v>
-      </c>
-      <c r="D4">
-        <v>0.2657999992370605</v>
-      </c>
-      <c r="E4">
-        <v>0.2300000041723251</v>
-      </c>
-      <c r="F4">
-        <v>0.2348999977111816</v>
-      </c>
-      <c r="G4">
-        <v>0.2398000061511993</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B5">
-        <v>0.2181999981403351</v>
-      </c>
-      <c r="C5">
-        <v>0.225600004196167</v>
-      </c>
-      <c r="D5">
-        <v>0.2599999904632568</v>
-      </c>
-      <c r="E5">
-        <v>0.2398999929428101</v>
-      </c>
-      <c r="F5">
-        <v>0.2260999977588654</v>
-      </c>
-      <c r="G5">
-        <v>0.2364999949932098</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" t="s">
-        <v>54</v>
-      </c>
       <c r="B6">
-        <v>0.1859000027179718</v>
+        <v>25</v>
       </c>
       <c r="C6">
-        <v>0.1787000000476837</v>
+        <v>3</v>
       </c>
       <c r="D6">
-        <v>0.1754000037908554</v>
-      </c>
-      <c r="E6">
-        <v>0.1729000061750412</v>
-      </c>
-      <c r="F6">
-        <v>0.1898999959230423</v>
-      </c>
-      <c r="G6">
-        <v>0.1782000064849854</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="B7">
-        <v>0.1831000000238419</v>
+        <v>125</v>
       </c>
       <c r="C7">
-        <v>0.1697999984025955</v>
+        <v>3.06</v>
       </c>
       <c r="D7">
-        <v>0.160300001502037</v>
-      </c>
-      <c r="E7">
-        <v>0.1678999960422516</v>
-      </c>
-      <c r="F7">
-        <v>0.1676999926567078</v>
-      </c>
-      <c r="G7">
-        <v>0.1701000034809113</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" t="s">
-        <v>65</v>
-      </c>
-      <c r="B8">
-        <v>0.120899997651577</v>
-      </c>
-      <c r="C8">
-        <v>0.1275999993085861</v>
-      </c>
-      <c r="D8">
-        <v>0.1372999995946884</v>
-      </c>
-      <c r="E8">
-        <v>0.1174999997019768</v>
-      </c>
-      <c r="F8">
-        <v>0.1319999992847443</v>
-      </c>
-      <c r="G8">
-        <v>0.1248999983072281</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" t="s">
-        <v>63</v>
-      </c>
-      <c r="B9">
-        <v>0.1220000013709068</v>
-      </c>
-      <c r="C9">
-        <v>0.120399996638298</v>
-      </c>
-      <c r="D9">
-        <v>0.1326999962329865</v>
-      </c>
-      <c r="E9">
-        <v>0.1234999969601631</v>
-      </c>
-      <c r="F9">
-        <v>0.1204999983310699</v>
-      </c>
-      <c r="G9">
-        <v>0.124600000679493</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" t="s">
-        <v>66</v>
-      </c>
-      <c r="B10">
-        <v>0.1085999980568886</v>
-      </c>
-      <c r="C10">
-        <v>0.1260000020265579</v>
-      </c>
-      <c r="D10">
-        <v>0.1324999928474426</v>
-      </c>
-      <c r="E10">
-        <v>0.121799997985363</v>
-      </c>
-      <c r="F10">
-        <v>0.1234999969601631</v>
-      </c>
-      <c r="G10">
-        <v>0.1216999962925911</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" t="s">
-        <v>56</v>
-      </c>
-      <c r="B11">
-        <v>0.1076000034809113</v>
-      </c>
-      <c r="C11">
-        <v>0.13230000436306</v>
-      </c>
-      <c r="D11">
-        <v>0.122699998319149</v>
-      </c>
-      <c r="E11">
-        <v>0.1036000028252602</v>
-      </c>
-      <c r="F11">
-        <v>0.09269999712705612</v>
-      </c>
-      <c r="G11">
-        <v>0.1123000010848045</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" t="s">
-        <v>62</v>
-      </c>
-      <c r="B12">
-        <v>0.08900000154972076</v>
-      </c>
-      <c r="C12">
-        <v>0.08179999887943268</v>
-      </c>
-      <c r="D12">
-        <v>0.09409999847412109</v>
-      </c>
-      <c r="E12">
-        <v>0.0917000025510788</v>
-      </c>
-      <c r="F12">
-        <v>0.1023000031709671</v>
-      </c>
-      <c r="G12">
-        <v>0.09070000052452087</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" t="s">
-        <v>59</v>
-      </c>
-      <c r="B13">
-        <v>0.09200000017881393</v>
-      </c>
-      <c r="C13">
-        <v>0.09049999713897705</v>
-      </c>
-      <c r="D13">
-        <v>0.08579999953508377</v>
-      </c>
-      <c r="E13">
-        <v>0.09149999916553497</v>
-      </c>
-      <c r="F13">
-        <v>0.09290000051259995</v>
-      </c>
-      <c r="G13">
-        <v>0.09030000120401382</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" t="s">
-        <v>64</v>
-      </c>
-      <c r="B14">
-        <v>0.06840000301599503</v>
-      </c>
-      <c r="C14">
-        <v>0.06859999895095825</v>
-      </c>
-      <c r="D14">
-        <v>0.08950000256299973</v>
-      </c>
-      <c r="E14">
-        <v>0.07209999859333038</v>
-      </c>
-      <c r="F14">
-        <v>0.07800000160932541</v>
-      </c>
-      <c r="G14">
-        <v>0.07490000128746033</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" t="s">
-        <v>61</v>
-      </c>
-      <c r="B15">
-        <v>0.06210000067949295</v>
-      </c>
-      <c r="C15">
-        <v>0.06949999928474426</v>
-      </c>
-      <c r="D15">
-        <v>0.07590000331401825</v>
-      </c>
-      <c r="E15">
-        <v>0.06060000136494637</v>
-      </c>
-      <c r="F15">
-        <v>0.06830000132322311</v>
-      </c>
-      <c r="G15">
-        <v>0.06599999964237213</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" t="s">
-        <v>68</v>
-      </c>
-      <c r="B16">
-        <v>0.05389999970793724</v>
-      </c>
-      <c r="C16">
-        <v>0.05770000070333481</v>
-      </c>
-      <c r="D16">
-        <v>0.05620000138878822</v>
-      </c>
-      <c r="E16">
-        <v>0.05490000173449516</v>
-      </c>
-      <c r="F16">
-        <v>0.05510000139474869</v>
-      </c>
-      <c r="G16">
-        <v>0.05539999902248383</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" t="s">
-        <v>67</v>
-      </c>
-      <c r="B17">
-        <v>0.02950000017881393</v>
-      </c>
-      <c r="C17">
-        <v>0.02649999968707561</v>
-      </c>
-      <c r="D17">
-        <v>0.02879999950528145</v>
-      </c>
-      <c r="E17">
-        <v>0.02879999950528145</v>
-      </c>
-      <c r="F17">
-        <v>0.0272000003606081</v>
-      </c>
-      <c r="G17">
-        <v>0.02859999984502792</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" t="s">
-        <v>58</v>
-      </c>
-      <c r="B18">
-        <v>0</v>
-      </c>
-      <c r="C18">
-        <v>0</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
+        <v>0.49</v>
       </c>
     </row>
   </sheetData>
@@ -6505,22 +6750,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>339</v>
+        <v>389</v>
       </c>
       <c r="B1" t="s">
-        <v>334</v>
+        <v>384</v>
       </c>
       <c r="C1" t="s">
-        <v>335</v>
+        <v>385</v>
       </c>
       <c r="D1" t="s">
-        <v>336</v>
+        <v>386</v>
       </c>
       <c r="E1" t="s">
-        <v>337</v>
+        <v>387</v>
       </c>
       <c r="F1" t="s">
-        <v>338</v>
+        <v>388</v>
       </c>
     </row>
     <row r="2" spans="1:6">
